--- a/report_forms/050_marina_daily_journal_form--report_forms.xlsx
+++ b/report_forms/050_marina_daily_journal_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vessel Length</t>
+          <t>Vessel Length In Feet</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prophets Depth</t>
+          <t>Prophets Depth In Feet</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>vessel_draft_type</t>
+          <t>vessel_draft_type_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>vessel_type_description</t>
+          <t>vessel_type_description_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vessel Type Description</t>
+          <t>Vessel Type Description 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>vessel_type</t>
+          <t>vessel_type_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vessel Type</t>
+          <t>Vessel Type 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>vessel_draft_depth</t>
+          <t>vessel_draft_depth_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1380,80 +1380,80 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vessel_draft_choices</t>
+          <t>vessel_draft_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>bow</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bow</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vessel_draft_choices</t>
+          <t>vessel_draft_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>stern</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Stern</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vessel_draft_type_choices</t>
+          <t>vessel_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bow</t>
+          <t>monohull</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Monohull</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vessel_draft_type_choices</t>
+          <t>vessel_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>stern</t>
+          <t>double_hull</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stern</t>
+          <t>Double Hull</t>
         </is>
       </c>
     </row>
@@ -1465,146 +1465,112 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>monohull</t>
+          <t>single_hull</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monohull</t>
+          <t>Single Hull</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vessel_type_choices</t>
+          <t>vessel_draft_type_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>double_hull</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Double Hull</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vessel_type_choices</t>
+          <t>vessel_draft_type_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>single_hull</t>
+          <t>freeboard</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Single Hull</t>
+          <t>Freeboard</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>vessel_draft_type_choices</t>
+          <t>vessel_draft_depth_type_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>forward</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Forward</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>vessel_draft_type_choices</t>
+          <t>vessel_draft_depth_type_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>freeboard</t>
+          <t>aft</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Freeboard</t>
+          <t>Aft</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vessel_draft_depth_type_choices</t>
+          <t>vessel_type_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>forward</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Sailboat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>vessel_draft_depth_type_choices</t>
+          <t>vessel_type_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>aft</t>
+          <t>yacht</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>Aft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>vessel_type_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sailboat</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Sailboat</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>vessel_type_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yacht</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Yacht</t>
         </is>
